--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV14_veto3_state_audit_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV14_veto3_state_audit_data.xlsx
@@ -447,7 +447,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -534,19 +534,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>89.94786575431736</v>
+        <v>94.73769957640926</v>
       </c>
       <c r="C3" t="n">
-        <v>7.363962202671879</v>
+        <v>3.877484522645813</v>
       </c>
       <c r="D3" t="n">
-        <v>1.026392961876833</v>
+        <v>0.7983056370153144</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9286412512218964</v>
+        <v>0.04887585532746823</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3421309872922776</v>
+        <v>0.1466275659824047</v>
       </c>
       <c r="G3" t="n">
         <v>0.3910068426197458</v>
@@ -559,13 +559,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95.43825350276963</v>
+        <v>99.1365265558814</v>
       </c>
       <c r="C4" t="n">
-        <v>4.154447702834799</v>
+        <v>0.8634734441186055</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4072987943955687</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86.88497882046269</v>
+        <v>87.42261322906484</v>
       </c>
       <c r="C8" t="n">
-        <v>9.058325187357445</v>
+        <v>2.981427174975562</v>
       </c>
       <c r="D8" t="n">
         <v>1.058976865428478</v>
       </c>
       <c r="E8" t="n">
-        <v>1.775822743564679</v>
+        <v>5.897686542847834</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7168458781362007</v>
+        <v>1.971326164874552</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5050505050505051</v>
+        <v>0.6679700228087325</v>
       </c>
     </row>
     <row r="9">
@@ -684,13 +684,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93.62984685565331</v>
+        <v>98.27305311176279</v>
       </c>
       <c r="C9" t="n">
-        <v>5.88139459107201</v>
+        <v>1.726946888237211</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4887585532746823</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>88.10687520364939</v>
+        <v>86.77093515803193</v>
       </c>
       <c r="C11" t="n">
         <v>2.036493971977843</v>
@@ -743,13 +743,13 @@
         <v>0.8308895405669598</v>
       </c>
       <c r="E11" t="n">
-        <v>5.848810687520365</v>
+        <v>8.031932225480611</v>
       </c>
       <c r="F11" t="n">
-        <v>1.955034213098729</v>
+        <v>1.319648093841642</v>
       </c>
       <c r="G11" t="n">
-        <v>1.221896383186706</v>
+        <v>1.01010101010101</v>
       </c>
     </row>
     <row r="12">
@@ -759,22 +759,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>87.4714890843923</v>
+        <v>95.04724666014988</v>
       </c>
       <c r="C12" t="n">
-        <v>10.28022157054415</v>
+        <v>3.372434017595308</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9612251547735419</v>
+        <v>0.4235907461713913</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4235907461713913</v>
+        <v>0.4072987943955687</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2932551319648094</v>
+        <v>0.3095470837406321</v>
       </c>
       <c r="G12" t="n">
-        <v>0.570218312153796</v>
+        <v>0.4398826979472141</v>
       </c>
     </row>
     <row r="13">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>95.74780058651027</v>
+        <v>96.70902574128381</v>
       </c>
       <c r="C14" t="n">
-        <v>2.899967416096449</v>
+        <v>2.117953730856957</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7494297816878462</v>
+        <v>0.570218312153796</v>
       </c>
       <c r="E14" t="n">
         <v>0.04887585532746823</v>
@@ -1091,22 +1091,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1216,22 +1216,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E8" t="n">
+        <v>17</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
         <v>4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -1241,22 +1241,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>2</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1297,13 +1297,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
         <v>3</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
@@ -1331,7 +1331,7 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -1381,7 +1381,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.46953405017921</v>
+        <v>5.865102639296188</v>
       </c>
       <c r="C3" t="n">
-        <v>7.363962202671879</v>
+        <v>3.877484522645813</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9286412512218964</v>
+        <v>0.04887585532746823</v>
       </c>
     </row>
     <row r="4">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.757249918540241</v>
+        <v>0.7983056370153144</v>
       </c>
       <c r="C4" t="n">
-        <v>4.154447702834799</v>
+        <v>0.8634734441186055</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1543,13 +1543,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12.93580971000326</v>
+        <v>5.588139459107201</v>
       </c>
       <c r="C8" t="n">
-        <v>9.058325187357445</v>
+        <v>2.981427174975562</v>
       </c>
       <c r="D8" t="n">
-        <v>1.775822743564679</v>
+        <v>5.897686542847834</v>
       </c>
     </row>
     <row r="9">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.559465623981754</v>
+        <v>1.922450309547084</v>
       </c>
       <c r="C9" t="n">
-        <v>5.88139459107201</v>
+        <v>1.726946888237211</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>2.036493971977843</v>
       </c>
       <c r="D11" t="n">
-        <v>5.848810687520365</v>
+        <v>8.031932225480611</v>
       </c>
     </row>
     <row r="12">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11.68132942326491</v>
+        <v>3.698273053111763</v>
       </c>
       <c r="C12" t="n">
-        <v>10.28022157054415</v>
+        <v>3.372434017595308</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4235907461713913</v>
+        <v>0.4072987943955687</v>
       </c>
     </row>
     <row r="13">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.969045291625937</v>
+        <v>3.86119257086999</v>
       </c>
       <c r="C14" t="n">
-        <v>2.899967416096449</v>
+        <v>2.117953730856957</v>
       </c>
       <c r="D14" t="n">
         <v>0.04887585532746823</v>

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV14_veto3_state_audit_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV14_veto3_state_audit_data.xlsx
@@ -447,7 +447,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>86.77093515803193</v>
+        <v>86.78722710980776</v>
       </c>
       <c r="C11" t="n">
         <v>2.036493971977843</v>
@@ -743,10 +743,10 @@
         <v>0.8308895405669598</v>
       </c>
       <c r="E11" t="n">
-        <v>8.031932225480611</v>
+        <v>7.917888563049853</v>
       </c>
       <c r="F11" t="n">
-        <v>1.319648093841642</v>
+        <v>1.417399804496579</v>
       </c>
       <c r="G11" t="n">
         <v>1.01010101010101</v>
@@ -1597,7 +1597,7 @@
         <v>2.036493971977843</v>
       </c>
       <c r="D11" t="n">
-        <v>8.031932225480611</v>
+        <v>7.917888563049853</v>
       </c>
     </row>
     <row r="12">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV14_veto3_state_audit_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV14_veto3_state_audit_data.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="state_dist" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="veto3_rate" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="transitions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1_v11_state_compare" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coactivation_DO_2_3" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +447,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-8fdd3599890f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1420,248 +1420,144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>v1_cooldown_pct</t>
+          <t>veto_freeze</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>v11_refractory_pct</t>
+          <t>veto_regime</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>v11_sustained_pct</t>
+          <t>veto3_signal</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>sustained</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Refractory</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>DO_1_1</t>
+          <t>veto_freeze</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.001955034213098729</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>DO_1_2</t>
+          <t>veto_regime</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.865102639296188</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>3.877484522645813</v>
+        <v>0.02346041055718475</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04887585532746823</v>
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0166177908113392</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.01743238840013034</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>DO_1_3</t>
+          <t>veto3_signal</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7983056370153144</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8634734441186055</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DO_1_4</t>
+          <t>sustained</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.0166177908113392</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.08927989573150863</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.01058976865428478</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>DO_2_1</t>
+          <t>Refractory</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.01743238840013034</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>DO_2_2</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>DO_2_3</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5.588139459107201</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2.981427174975562</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5.897686542847834</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>DO_2_4</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.922450309547084</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.726946888237211</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>ORP_1_1</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>ORP_1_2</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>16.42228739002933</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2.036493971977843</v>
-      </c>
-      <c r="D11" t="n">
-        <v>7.917888563049853</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>ORP_1_3</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3.698273053111763</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.372434017595308</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.4072987943955687</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ORP_2_1</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>ORP_2_2</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3.86119257086999</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2.117953730856957</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.04887585532746823</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>ORP_2_3</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
+      <c r="E6" t="n">
+        <v>0.01058976865428478</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.04040404040404041</v>
       </c>
     </row>
   </sheetData>

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV14_veto3_state_audit_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV14_veto3_state_audit_data.xlsx
@@ -447,7 +447,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-8fdd3599890f</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
